--- a/src/staticfiles/study/templates/fact_mappings_import_template.xlsx
+++ b/src/staticfiles/study/templates/fact_mappings_import_template.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:AK2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -499,6 +499,141 @@
           <t>Display Order</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Attestation Policy Code</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Attestation Action Kind</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Attestation Gate Code</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Attestation Display Order</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Attestation Statement Code</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Attestation Statement Version</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Attestation Permission Code</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Attestation Role Code</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Attestation Delegation Task Code</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Attestation Condition Code</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Attestation Requires Confirmation</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Attestation Requires Signature</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Attestation Requires Reauth</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Attestation Invalidate On Data Change</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Attestation Invalidate On Scope Change</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Attestation Required For Lock</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Attestation Enabled</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Attestation Dialog Title Vi</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Attestation Action Label Vi</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Attestation Statement Text Vi</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Attestation Confirmation Label Vi</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Attestation Success Message Vi</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Attestation Dialog Title En</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>Attestation Action Label En</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>Attestation Statement Text En</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>Attestation Confirmation Label En</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>Attestation Success Message En</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -531,13 +666,11 @@
           <t>is_true</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
         <v>1</v>
       </c>

--- a/src/staticfiles/study/templates/fact_mappings_import_template.xlsx
+++ b/src/staticfiles/study/templates/fact_mappings_import_template.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -499,141 +499,6 @@
           <t>Display Order</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Attestation Policy Code</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Attestation Action Kind</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Attestation Gate Code</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Attestation Display Order</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Attestation Statement Code</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Attestation Statement Version</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Attestation Permission Code</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Attestation Role Code</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Attestation Delegation Task Code</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Attestation Condition Code</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Attestation Requires Confirmation</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Attestation Requires Signature</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Attestation Requires Reauth</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Attestation Invalidate On Data Change</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Attestation Invalidate On Scope Change</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>Attestation Required For Lock</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>Attestation Enabled</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>Attestation Dialog Title Vi</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>Attestation Action Label Vi</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>Attestation Statement Text Vi</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>Attestation Confirmation Label Vi</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>Attestation Success Message Vi</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>Attestation Dialog Title En</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>Attestation Action Label En</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>Attestation Statement Text En</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>Attestation Confirmation Label En</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>Attestation Success Message En</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
